--- a/100_keywords_freq.xlsx
+++ b/100_keywords_freq.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0909\web---vue_backup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CF0CE32-FFD7-44F5-AAD2-68C6AAC3E81C}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93406BD3-CB7D-4118-B7AE-9637B5A2AB1A}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17268" windowHeight="5496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -751,8 +751,8 @@
         <v>79270</v>
       </c>
       <c r="C2" s="4">
-        <f>ROUND((B2/156908)*10000, 2)</f>
-        <v>5052</v>
+        <f>ROUND((B2/5770465)*100000, 0)</f>
+        <v>1374</v>
       </c>
       <c r="D2" s="5"/>
     </row>
@@ -764,8 +764,8 @@
         <v>68078</v>
       </c>
       <c r="C3" s="4">
-        <f t="shared" ref="C3:C66" si="0">ROUND((B3/156908)*10000, 2)</f>
-        <v>4338.72</v>
+        <f t="shared" ref="C3:C66" si="0">ROUND((B3/5770465)*100000, 0)</f>
+        <v>1180</v>
       </c>
       <c r="D3" s="5"/>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="C4" s="4">
         <f t="shared" si="0"/>
-        <v>4211.8900000000003</v>
+        <v>1145</v>
       </c>
       <c r="D4" s="5"/>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="C5" s="4">
         <f t="shared" si="0"/>
-        <v>4052.44</v>
+        <v>1102</v>
       </c>
       <c r="D5" s="5"/>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="C6" s="4">
         <f t="shared" si="0"/>
-        <v>3657.3</v>
+        <v>994</v>
       </c>
       <c r="D6" s="5"/>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="C7" s="4">
         <f t="shared" si="0"/>
-        <v>3167.4</v>
+        <v>861</v>
       </c>
       <c r="D7" s="5"/>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="C8" s="4">
         <f t="shared" si="0"/>
-        <v>3019.35</v>
+        <v>821</v>
       </c>
       <c r="D8" s="5"/>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="C9" s="4">
         <f t="shared" si="0"/>
-        <v>2944.72</v>
+        <v>801</v>
       </c>
       <c r="D9" s="5"/>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="C10" s="4">
         <f t="shared" si="0"/>
-        <v>2880.54</v>
+        <v>783</v>
       </c>
       <c r="D10" s="5"/>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="C11" s="4">
         <f t="shared" si="0"/>
-        <v>2832.49</v>
+        <v>770</v>
       </c>
       <c r="D11" s="5"/>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="C12" s="4">
         <f t="shared" si="0"/>
-        <v>2608.98</v>
+        <v>709</v>
       </c>
       <c r="D12" s="5"/>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="C13" s="4">
         <f t="shared" si="0"/>
-        <v>2196.38</v>
+        <v>597</v>
       </c>
       <c r="D13" s="5"/>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="C14" s="4">
         <f t="shared" si="0"/>
-        <v>2054.77</v>
+        <v>559</v>
       </c>
       <c r="D14" s="5"/>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C15" s="4">
         <f t="shared" si="0"/>
-        <v>2048.91</v>
+        <v>557</v>
       </c>
       <c r="D15" s="5"/>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="C16" s="4">
         <f t="shared" si="0"/>
-        <v>1989.13</v>
+        <v>541</v>
       </c>
       <c r="D16" s="5"/>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="C17" s="4">
         <f t="shared" si="0"/>
-        <v>1961.28</v>
+        <v>533</v>
       </c>
       <c r="D17" s="5"/>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="C18" s="4">
         <f t="shared" si="0"/>
-        <v>1822.21</v>
+        <v>495</v>
       </c>
       <c r="D18" s="5"/>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="C19" s="4">
         <f t="shared" si="0"/>
-        <v>1810.3</v>
+        <v>492</v>
       </c>
       <c r="D19" s="5"/>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="C20" s="4">
         <f t="shared" si="0"/>
-        <v>1792.71</v>
+        <v>487</v>
       </c>
       <c r="D20" s="5"/>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C21" s="4">
         <f t="shared" si="0"/>
-        <v>1725.09</v>
+        <v>469</v>
       </c>
       <c r="D21" s="5"/>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="C22" s="4">
         <f t="shared" si="0"/>
-        <v>1613.3</v>
+        <v>439</v>
       </c>
       <c r="D22" s="5"/>
     </row>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="C23" s="4">
         <f t="shared" si="0"/>
-        <v>1569.26</v>
+        <v>427</v>
       </c>
       <c r="D23" s="5"/>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C24" s="4">
         <f t="shared" si="0"/>
-        <v>1539.82</v>
+        <v>419</v>
       </c>
       <c r="D24" s="5"/>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="C25" s="4">
         <f t="shared" si="0"/>
-        <v>1465.51</v>
+        <v>398</v>
       </c>
       <c r="D25" s="5"/>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="C26" s="4">
         <f t="shared" si="0"/>
-        <v>1436.7</v>
+        <v>391</v>
       </c>
       <c r="D26" s="5"/>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C27" s="4">
         <f t="shared" si="0"/>
-        <v>1373.8</v>
+        <v>374</v>
       </c>
       <c r="D27" s="5"/>
     </row>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="C28" s="4">
         <f t="shared" si="0"/>
-        <v>1360.03</v>
+        <v>370</v>
       </c>
       <c r="D28" s="5"/>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="C29" s="4">
         <f t="shared" si="0"/>
-        <v>1343.53</v>
+        <v>365</v>
       </c>
       <c r="D29" s="5"/>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="C30" s="4">
         <f t="shared" si="0"/>
-        <v>1337.54</v>
+        <v>364</v>
       </c>
       <c r="D30" s="5"/>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="C31" s="4">
         <f t="shared" si="0"/>
-        <v>1300.6300000000001</v>
+        <v>354</v>
       </c>
       <c r="D31" s="5"/>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="C32" s="4">
         <f t="shared" si="0"/>
-        <v>1210.26</v>
+        <v>329</v>
       </c>
       <c r="D32" s="5"/>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C33" s="4">
         <f t="shared" si="0"/>
-        <v>1181.01</v>
+        <v>321</v>
       </c>
       <c r="D33" s="5"/>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="C34" s="4">
         <f t="shared" si="0"/>
-        <v>1156.79</v>
+        <v>315</v>
       </c>
       <c r="D34" s="5"/>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="C35" s="4">
         <f t="shared" si="0"/>
-        <v>1118.04</v>
+        <v>304</v>
       </c>
       <c r="D35" s="5"/>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="C36" s="4">
         <f t="shared" si="0"/>
-        <v>1105.3</v>
+        <v>301</v>
       </c>
       <c r="D36" s="5"/>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="C37" s="4">
         <f t="shared" si="0"/>
-        <v>1089.43</v>
+        <v>296</v>
       </c>
       <c r="D37" s="5"/>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="C38" s="4">
         <f t="shared" si="0"/>
-        <v>1079.23</v>
+        <v>293</v>
       </c>
       <c r="D38" s="5"/>
     </row>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="C39" s="4">
         <f t="shared" si="0"/>
-        <v>1011.61</v>
+        <v>275</v>
       </c>
       <c r="D39" s="5"/>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="C40" s="4">
         <f t="shared" si="0"/>
-        <v>994.4</v>
+        <v>270</v>
       </c>
       <c r="D40" s="5"/>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="C41" s="4">
         <f t="shared" si="0"/>
-        <v>992.49</v>
+        <v>270</v>
       </c>
       <c r="D41" s="5"/>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C42" s="4">
         <f t="shared" si="0"/>
-        <v>980.57</v>
+        <v>267</v>
       </c>
       <c r="D42" s="5"/>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C43" s="4">
         <f t="shared" si="0"/>
-        <v>971.59</v>
+        <v>264</v>
       </c>
       <c r="D43" s="5"/>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C44" s="4">
         <f t="shared" si="0"/>
-        <v>964.83</v>
+        <v>262</v>
       </c>
       <c r="D44" s="5"/>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C45" s="4">
         <f t="shared" si="0"/>
-        <v>955.66</v>
+        <v>260</v>
       </c>
       <c r="D45" s="5"/>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="C46" s="4">
         <f t="shared" si="0"/>
-        <v>933.92</v>
+        <v>254</v>
       </c>
       <c r="D46" s="5"/>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C47" s="4">
         <f t="shared" si="0"/>
-        <v>927.42</v>
+        <v>252</v>
       </c>
       <c r="D47" s="5"/>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="C48" s="4">
         <f t="shared" si="0"/>
-        <v>927.29</v>
+        <v>252</v>
       </c>
       <c r="D48" s="5"/>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="C49" s="4">
         <f t="shared" si="0"/>
-        <v>918.95</v>
+        <v>250</v>
       </c>
       <c r="D49" s="5"/>
     </row>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="C50" s="4">
         <f t="shared" si="0"/>
-        <v>912.51</v>
+        <v>248</v>
       </c>
       <c r="D50" s="5"/>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C51" s="4">
         <f t="shared" si="0"/>
-        <v>903.4</v>
+        <v>246</v>
       </c>
       <c r="D51" s="5"/>
     </row>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="C52" s="4">
         <f t="shared" si="0"/>
-        <v>878.03</v>
+        <v>239</v>
       </c>
       <c r="D52" s="5"/>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="C53" s="4">
         <f t="shared" si="0"/>
-        <v>876.82</v>
+        <v>238</v>
       </c>
       <c r="D53" s="5"/>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C54" s="4">
         <f t="shared" si="0"/>
-        <v>830.42</v>
+        <v>226</v>
       </c>
       <c r="D54" s="5"/>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="C55" s="4">
         <f t="shared" si="0"/>
-        <v>827.62</v>
+        <v>225</v>
       </c>
       <c r="D55" s="5"/>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C56" s="4">
         <f t="shared" si="0"/>
-        <v>827.49</v>
+        <v>225</v>
       </c>
       <c r="D56" s="5"/>
     </row>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C57" s="4">
         <f t="shared" si="0"/>
-        <v>827.36</v>
+        <v>225</v>
       </c>
       <c r="D57" s="5"/>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="C58" s="4">
         <f t="shared" si="0"/>
-        <v>814.49</v>
+        <v>221</v>
       </c>
       <c r="D58" s="5"/>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C59" s="4">
         <f t="shared" si="0"/>
-        <v>811.62</v>
+        <v>221</v>
       </c>
       <c r="D59" s="5"/>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="C60" s="4">
         <f t="shared" si="0"/>
-        <v>800.92</v>
+        <v>218</v>
       </c>
       <c r="D60" s="5"/>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="C61" s="4">
         <f t="shared" si="0"/>
-        <v>787.47</v>
+        <v>214</v>
       </c>
       <c r="D61" s="5"/>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="C62" s="4">
         <f t="shared" si="0"/>
-        <v>768.35</v>
+        <v>209</v>
       </c>
       <c r="D62" s="5"/>
     </row>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="C63" s="4">
         <f t="shared" si="0"/>
-        <v>758.41</v>
+        <v>206</v>
       </c>
       <c r="D63" s="5"/>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="C64" s="4">
         <f t="shared" si="0"/>
-        <v>725.39</v>
+        <v>197</v>
       </c>
       <c r="D64" s="5"/>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="C65" s="4">
         <f t="shared" si="0"/>
-        <v>719.85</v>
+        <v>196</v>
       </c>
       <c r="D65" s="5"/>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="C66" s="4">
         <f t="shared" si="0"/>
-        <v>715.64</v>
+        <v>195</v>
       </c>
       <c r="D66" s="5"/>
     </row>
@@ -1596,8 +1596,8 @@
         <v>10960</v>
       </c>
       <c r="C67" s="4">
-        <f t="shared" ref="C67:C101" si="1">ROUND((B67/156908)*10000, 2)</f>
-        <v>698.5</v>
+        <f t="shared" ref="C67:C101" si="1">ROUND((B67/5770465)*100000, 0)</f>
+        <v>190</v>
       </c>
       <c r="D67" s="5"/>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="C68" s="4">
         <f t="shared" si="1"/>
-        <v>692.13</v>
+        <v>188</v>
       </c>
       <c r="D68" s="5"/>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C69" s="4">
         <f t="shared" si="1"/>
-        <v>691.81</v>
+        <v>188</v>
       </c>
       <c r="D69" s="5"/>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="C70" s="4">
         <f t="shared" si="1"/>
-        <v>683.39</v>
+        <v>186</v>
       </c>
       <c r="D70" s="5"/>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="C71" s="4">
         <f t="shared" si="1"/>
-        <v>667.33</v>
+        <v>181</v>
       </c>
       <c r="D71" s="5"/>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C72" s="4">
         <f t="shared" si="1"/>
-        <v>665.61</v>
+        <v>181</v>
       </c>
       <c r="D72" s="5"/>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="C73" s="4">
         <f t="shared" si="1"/>
-        <v>646.67999999999995</v>
+        <v>176</v>
       </c>
       <c r="D73" s="5"/>
     </row>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="C74" s="4">
         <f t="shared" si="1"/>
-        <v>644.52</v>
+        <v>175</v>
       </c>
       <c r="D74" s="5"/>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="C75" s="4">
         <f t="shared" si="1"/>
-        <v>634.96</v>
+        <v>173</v>
       </c>
       <c r="D75" s="5"/>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="C76" s="4">
         <f t="shared" si="1"/>
-        <v>626.29</v>
+        <v>170</v>
       </c>
       <c r="D76" s="5"/>
     </row>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="C77" s="4">
         <f t="shared" si="1"/>
-        <v>600.61</v>
+        <v>163</v>
       </c>
       <c r="D77" s="5"/>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="C78" s="4">
         <f t="shared" si="1"/>
-        <v>597.74</v>
+        <v>163</v>
       </c>
       <c r="D78" s="5"/>
     </row>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="C79" s="4">
         <f t="shared" si="1"/>
-        <v>593.09</v>
+        <v>161</v>
       </c>
       <c r="D79" s="5"/>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="C80" s="4">
         <f t="shared" si="1"/>
-        <v>591.67999999999995</v>
+        <v>161</v>
       </c>
       <c r="D80" s="5"/>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="C81" s="4">
         <f t="shared" si="1"/>
-        <v>567.72</v>
+        <v>154</v>
       </c>
       <c r="D81" s="5"/>
     </row>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="C82" s="4">
         <f t="shared" si="1"/>
-        <v>534.64</v>
+        <v>145</v>
       </c>
       <c r="D82" s="5"/>
     </row>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C83" s="4">
         <f t="shared" si="1"/>
-        <v>532.29</v>
+        <v>145</v>
       </c>
       <c r="D83" s="5"/>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="C84" s="4">
         <f t="shared" si="1"/>
-        <v>525.91</v>
+        <v>143</v>
       </c>
       <c r="D84" s="5"/>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="C85" s="4">
         <f t="shared" si="1"/>
-        <v>522.15</v>
+        <v>142</v>
       </c>
       <c r="D85" s="5"/>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="C86" s="4">
         <f t="shared" si="1"/>
-        <v>517.88</v>
+        <v>141</v>
       </c>
       <c r="D86" s="5"/>
     </row>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="C87" s="4">
         <f t="shared" si="1"/>
-        <v>509.41</v>
+        <v>139</v>
       </c>
       <c r="D87" s="5"/>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="C88" s="4">
         <f t="shared" si="1"/>
-        <v>507.69</v>
+        <v>138</v>
       </c>
       <c r="D88" s="5"/>
     </row>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="C89" s="4">
         <f t="shared" si="1"/>
-        <v>498.19</v>
+        <v>135</v>
       </c>
       <c r="D89" s="5"/>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="C90" s="4">
         <f t="shared" si="1"/>
-        <v>496.85</v>
+        <v>135</v>
       </c>
       <c r="D90" s="5"/>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="C91" s="4">
         <f t="shared" si="1"/>
-        <v>493.22</v>
+        <v>134</v>
       </c>
       <c r="D91" s="5"/>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C92" s="4">
         <f t="shared" si="1"/>
-        <v>486.91</v>
+        <v>132</v>
       </c>
       <c r="D92" s="5"/>
     </row>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C93" s="4">
         <f t="shared" si="1"/>
-        <v>476.71</v>
+        <v>130</v>
       </c>
       <c r="D93" s="5"/>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C94" s="4">
         <f t="shared" si="1"/>
-        <v>476.39</v>
+        <v>130</v>
       </c>
       <c r="D94" s="5"/>
     </row>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="C95" s="4">
         <f t="shared" si="1"/>
-        <v>473.4</v>
+        <v>129</v>
       </c>
       <c r="D95" s="5"/>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="C96" s="4">
         <f t="shared" si="1"/>
-        <v>468.04</v>
+        <v>127</v>
       </c>
       <c r="D96" s="5"/>
     </row>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="C97" s="4">
         <f t="shared" si="1"/>
-        <v>442.04</v>
+        <v>120</v>
       </c>
       <c r="D97" s="5"/>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="C98" s="4">
         <f t="shared" si="1"/>
-        <v>439.24</v>
+        <v>119</v>
       </c>
       <c r="D98" s="5"/>
     </row>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="C99" s="4">
         <f t="shared" si="1"/>
-        <v>436.05</v>
+        <v>119</v>
       </c>
       <c r="D99" s="5"/>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C100" s="4">
         <f t="shared" si="1"/>
-        <v>426.75</v>
+        <v>116</v>
       </c>
       <c r="D100" s="5"/>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="C101" s="4">
         <f t="shared" si="1"/>
-        <v>426.11</v>
+        <v>116</v>
       </c>
       <c r="D101" s="5"/>
     </row>

--- a/100_keywords_freq.xlsx
+++ b/100_keywords_freq.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0909\web---vue_backup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93406BD3-CB7D-4118-B7AE-9637B5A2AB1A}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF56F35C-2E6F-49A3-94B6-5983EE525577}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17268" windowHeight="5496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="179021" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
   <si>
     <t>word</t>
   </si>
@@ -328,7 +328,75 @@
     <t>驗證</t>
   </si>
   <si>
-    <t>RiskWeight</t>
+    <t>權重</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>平均值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>「高風險門檻」(Mean + 2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+        <charset val="161"/>
+      </rPr>
+      <t>σ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>樣本標準差</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中位數</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>「中風險門檻」(Mean +-0.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>σ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>區間驗證</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -336,7 +404,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -364,16 +432,48 @@
       <family val="1"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="161"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="1"/>
+      <charset val="161"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -405,26 +505,88 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -728,1424 +890,2280 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:S101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="7" max="7" width="9.625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D1" s="3"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1" s="8"/>
+      <c r="H1" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2">
         <v>79270</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="2">
         <f>ROUND((B2/5770465)*100000, 0)</f>
         <v>1374</v>
       </c>
-      <c r="D2" s="5"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D2" s="3">
+        <f>AVERAGE(C2:C101)</f>
+        <v>332</v>
+      </c>
+      <c r="E2" s="3">
+        <f>ROUND(MEDIAN(C2:C101),0)</f>
+        <v>243</v>
+      </c>
+      <c r="F2" s="9">
+        <f>ROUND(_xlfn.STDEV.S(C2:C101), 0)</f>
+        <v>259</v>
+      </c>
+      <c r="G2" s="9"/>
+      <c r="H2" s="6">
+        <f>ROUND(AVERAGE(C2:C101) + 2 * _xlfn.STDEV.S(C2:C101), 0)</f>
+        <v>849</v>
+      </c>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6">
+        <f>ROUND(_xlfn.QUARTILE.INC(C2:C101, 1), 0)</f>
+        <v>168</v>
+      </c>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="14" t="str">
+        <f>IF(C2&gt;=850, "高風險", IF(C2&gt;=168, "中風險", "低風險"))</f>
+        <v>高風險</v>
+      </c>
+      <c r="Q2" s="14"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3">
         <v>68078</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="2">
         <f t="shared" ref="C3:C66" si="0">ROUND((B3/5770465)*100000, 0)</f>
         <v>1180</v>
       </c>
-      <c r="D3" s="5"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="P3" s="14" t="str">
+        <f t="shared" ref="P3:P66" si="1">IF(C3&gt;=850, "高風險", IF(C3&gt;=168, "中風險", "低風險"))</f>
+        <v>高風險</v>
+      </c>
+      <c r="Q3" s="14"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4">
         <v>66088</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="2">
         <f t="shared" si="0"/>
         <v>1145</v>
       </c>
-      <c r="D4" s="5"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="P4" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>高風險</v>
+      </c>
+      <c r="Q4" s="14"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5">
         <v>63586</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="2">
         <f t="shared" si="0"/>
         <v>1102</v>
       </c>
-      <c r="D5" s="5"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="P5" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>高風險</v>
+      </c>
+      <c r="Q5" s="14"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6">
         <v>57386</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="2">
         <f t="shared" si="0"/>
         <v>994</v>
       </c>
-      <c r="D6" s="5"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="P6" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>高風險</v>
+      </c>
+      <c r="Q6" s="14"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
       <c r="B7">
         <v>49699</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="2">
         <f t="shared" si="0"/>
         <v>861</v>
       </c>
-      <c r="D7" s="5"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="P7" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>高風險</v>
+      </c>
+      <c r="Q7" s="14"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8">
         <v>47376</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="2">
         <f t="shared" si="0"/>
         <v>821</v>
       </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="P8" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q8" s="12"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9">
         <v>46205</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="2">
         <f t="shared" si="0"/>
         <v>801</v>
       </c>
-      <c r="D9" s="5"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="P9" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q9" s="12"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10">
         <v>45198</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="2">
         <f t="shared" si="0"/>
         <v>783</v>
       </c>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="P10" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q10" s="12"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="B11">
         <v>44444</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="2">
         <f t="shared" si="0"/>
         <v>770</v>
       </c>
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="P11" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q11" s="12"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
       <c r="B12">
         <v>40937</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="2">
         <f t="shared" si="0"/>
         <v>709</v>
       </c>
-      <c r="D12" s="5"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="P12" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q12" s="12"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
       <c r="B13">
         <v>34463</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="2">
         <f t="shared" si="0"/>
         <v>597</v>
       </c>
-      <c r="D13" s="5"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="P13" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q13" s="12"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14">
         <v>32241</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="2">
         <f t="shared" si="0"/>
         <v>559</v>
       </c>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="P14" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q14" s="12"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
       <c r="B15">
         <v>32149</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="2">
         <f t="shared" si="0"/>
         <v>557</v>
       </c>
-      <c r="D15" s="5"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="P15" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q15" s="12"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>16</v>
       </c>
       <c r="B16">
         <v>31211</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="2">
         <f t="shared" si="0"/>
         <v>541</v>
       </c>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="P16" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q16" s="12"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>17</v>
       </c>
       <c r="B17">
         <v>30774</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="2">
         <f t="shared" si="0"/>
         <v>533</v>
       </c>
-      <c r="D17" s="5"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="P17" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q17" s="12"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
       <c r="B18">
         <v>28592</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="2">
         <f t="shared" si="0"/>
         <v>495</v>
       </c>
-      <c r="D18" s="5"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="P18" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q18" s="12"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>19</v>
       </c>
       <c r="B19">
         <v>28405</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="2">
         <f t="shared" si="0"/>
         <v>492</v>
       </c>
-      <c r="D19" s="5"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="P19" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q19" s="12"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>20</v>
       </c>
       <c r="B20">
         <v>28129</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="2">
         <f t="shared" si="0"/>
         <v>487</v>
       </c>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="P20" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q20" s="12"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>21</v>
       </c>
       <c r="B21">
         <v>27068</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="2">
         <f t="shared" si="0"/>
         <v>469</v>
       </c>
-      <c r="D21" s="5"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="P21" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q21" s="12"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>22</v>
       </c>
       <c r="B22">
         <v>25314</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="2">
         <f t="shared" si="0"/>
         <v>439</v>
       </c>
-      <c r="D22" s="5"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="P22" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q22" s="12"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>23</v>
       </c>
       <c r="B23">
         <v>24623</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="2">
         <f t="shared" si="0"/>
         <v>427</v>
       </c>
-      <c r="D23" s="5"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="P23" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q23" s="12"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>24</v>
       </c>
       <c r="B24">
         <v>24161</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="2">
         <f t="shared" si="0"/>
         <v>419</v>
       </c>
-      <c r="D24" s="5"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="P24" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q24" s="12"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>25</v>
       </c>
       <c r="B25">
         <v>22995</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="2">
         <f t="shared" si="0"/>
         <v>398</v>
       </c>
-      <c r="D25" s="5"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="P25" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q25" s="12"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>26</v>
       </c>
       <c r="B26">
         <v>22543</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="2">
         <f t="shared" si="0"/>
         <v>391</v>
       </c>
-      <c r="D26" s="5"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="P26" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q26" s="12"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>27</v>
       </c>
       <c r="B27">
         <v>21556</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="2">
         <f t="shared" si="0"/>
         <v>374</v>
       </c>
-      <c r="D27" s="5"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="P27" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q27" s="12"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>28</v>
       </c>
       <c r="B28">
         <v>21340</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="2">
         <f t="shared" si="0"/>
         <v>370</v>
       </c>
-      <c r="D28" s="5"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="P28" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q28" s="12"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>29</v>
       </c>
       <c r="B29">
         <v>21081</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="2">
         <f t="shared" si="0"/>
         <v>365</v>
       </c>
-      <c r="D29" s="5"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="P29" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q29" s="12"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>30</v>
       </c>
       <c r="B30">
         <v>20987</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="2">
         <f t="shared" si="0"/>
         <v>364</v>
       </c>
-      <c r="D30" s="5"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="P30" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q30" s="12"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>31</v>
       </c>
       <c r="B31">
         <v>20408</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="2">
         <f t="shared" si="0"/>
         <v>354</v>
       </c>
-      <c r="D31" s="5"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="P31" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q31" s="12"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>32</v>
       </c>
       <c r="B32">
         <v>18990</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="2">
         <f t="shared" si="0"/>
         <v>329</v>
       </c>
-      <c r="D32" s="5"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="P32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q32" s="12"/>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>33</v>
       </c>
       <c r="B33">
         <v>18531</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33" s="2">
         <f t="shared" si="0"/>
         <v>321</v>
       </c>
-      <c r="D33" s="5"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="P33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q33" s="12"/>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>34</v>
       </c>
       <c r="B34">
         <v>18151</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="2">
         <f t="shared" si="0"/>
         <v>315</v>
       </c>
-      <c r="D34" s="5"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="P34" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q34" s="12"/>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>35</v>
       </c>
       <c r="B35">
         <v>17543</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="2">
         <f t="shared" si="0"/>
         <v>304</v>
       </c>
-      <c r="D35" s="5"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="P35" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q35" s="12"/>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>36</v>
       </c>
       <c r="B36">
         <v>17343</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="2">
         <f t="shared" si="0"/>
         <v>301</v>
       </c>
-      <c r="D36" s="5"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="P36" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q36" s="12"/>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>37</v>
       </c>
       <c r="B37">
         <v>17094</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37" s="2">
         <f t="shared" si="0"/>
         <v>296</v>
       </c>
-      <c r="D37" s="5"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="P37" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q37" s="12"/>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>38</v>
       </c>
       <c r="B38">
         <v>16934</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38" s="2">
         <f t="shared" si="0"/>
         <v>293</v>
       </c>
-      <c r="D38" s="5"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="P38" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q38" s="12"/>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>39</v>
       </c>
       <c r="B39">
         <v>15873</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C39" s="2">
         <f t="shared" si="0"/>
         <v>275</v>
       </c>
-      <c r="D39" s="5"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="P39" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q39" s="12"/>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>40</v>
       </c>
       <c r="B40">
         <v>15603</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="2">
         <f t="shared" si="0"/>
         <v>270</v>
       </c>
-      <c r="D40" s="5"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="P40" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q40" s="12"/>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>41</v>
       </c>
       <c r="B41">
         <v>15573</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="2">
         <f t="shared" si="0"/>
         <v>270</v>
       </c>
-      <c r="D41" s="5"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="P41" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q41" s="12"/>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>42</v>
       </c>
       <c r="B42">
         <v>15386</v>
       </c>
-      <c r="C42" s="4">
+      <c r="C42" s="2">
         <f t="shared" si="0"/>
         <v>267</v>
       </c>
-      <c r="D42" s="5"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="P42" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q42" s="12"/>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>43</v>
       </c>
       <c r="B43">
         <v>15245</v>
       </c>
-      <c r="C43" s="4">
+      <c r="C43" s="2">
         <f t="shared" si="0"/>
         <v>264</v>
       </c>
-      <c r="D43" s="5"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="P43" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q43" s="12"/>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>44</v>
       </c>
       <c r="B44">
         <v>15139</v>
       </c>
-      <c r="C44" s="4">
+      <c r="C44" s="2">
         <f t="shared" si="0"/>
         <v>262</v>
       </c>
-      <c r="D44" s="5"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="P44" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q44" s="12"/>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>45</v>
       </c>
       <c r="B45">
         <v>14995</v>
       </c>
-      <c r="C45" s="4">
+      <c r="C45" s="2">
         <f t="shared" si="0"/>
         <v>260</v>
       </c>
-      <c r="D45" s="5"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="P45" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q45" s="12"/>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>46</v>
       </c>
       <c r="B46">
         <v>14654</v>
       </c>
-      <c r="C46" s="4">
+      <c r="C46" s="2">
         <f t="shared" si="0"/>
         <v>254</v>
       </c>
-      <c r="D46" s="5"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="P46" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q46" s="12"/>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>47</v>
       </c>
       <c r="B47">
         <v>14552</v>
       </c>
-      <c r="C47" s="4">
+      <c r="C47" s="2">
         <f t="shared" si="0"/>
         <v>252</v>
       </c>
-      <c r="D47" s="5"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="P47" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q47" s="12"/>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>48</v>
       </c>
       <c r="B48">
         <v>14550</v>
       </c>
-      <c r="C48" s="4">
+      <c r="C48" s="2">
         <f t="shared" si="0"/>
         <v>252</v>
       </c>
-      <c r="D48" s="5"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="P48" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q48" s="12"/>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>49</v>
       </c>
       <c r="B49">
         <v>14419</v>
       </c>
-      <c r="C49" s="4">
+      <c r="C49" s="2">
         <f t="shared" si="0"/>
         <v>250</v>
       </c>
-      <c r="D49" s="5"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="P49" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q49" s="12"/>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>50</v>
       </c>
       <c r="B50">
         <v>14318</v>
       </c>
-      <c r="C50" s="4">
+      <c r="C50" s="2">
         <f t="shared" si="0"/>
         <v>248</v>
       </c>
-      <c r="D50" s="5"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="P50" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q50" s="12"/>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>51</v>
       </c>
       <c r="B51">
         <v>14175</v>
       </c>
-      <c r="C51" s="4">
+      <c r="C51" s="2">
         <f t="shared" si="0"/>
         <v>246</v>
       </c>
-      <c r="D51" s="5"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="P51" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q51" s="12"/>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>52</v>
       </c>
       <c r="B52">
         <v>13777</v>
       </c>
-      <c r="C52" s="4">
+      <c r="C52" s="2">
         <f t="shared" si="0"/>
         <v>239</v>
       </c>
-      <c r="D52" s="5"/>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="P52" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q52" s="12"/>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>53</v>
       </c>
       <c r="B53">
         <v>13758</v>
       </c>
-      <c r="C53" s="4">
+      <c r="C53" s="2">
         <f t="shared" si="0"/>
         <v>238</v>
       </c>
-      <c r="D53" s="5"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="P53" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q53" s="12"/>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>54</v>
       </c>
       <c r="B54">
         <v>13030</v>
       </c>
-      <c r="C54" s="4">
+      <c r="C54" s="2">
         <f t="shared" si="0"/>
         <v>226</v>
       </c>
-      <c r="D54" s="5"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="P54" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q54" s="12"/>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>55</v>
       </c>
       <c r="B55">
         <v>12986</v>
       </c>
-      <c r="C55" s="4">
+      <c r="C55" s="2">
         <f t="shared" si="0"/>
         <v>225</v>
       </c>
-      <c r="D55" s="5"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="P55" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q55" s="12"/>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>56</v>
       </c>
       <c r="B56">
         <v>12984</v>
       </c>
-      <c r="C56" s="4">
+      <c r="C56" s="2">
         <f t="shared" si="0"/>
         <v>225</v>
       </c>
-      <c r="D56" s="5"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="P56" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q56" s="12"/>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>57</v>
       </c>
       <c r="B57">
         <v>12982</v>
       </c>
-      <c r="C57" s="4">
+      <c r="C57" s="2">
         <f t="shared" si="0"/>
         <v>225</v>
       </c>
-      <c r="D57" s="5"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="P57" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q57" s="12"/>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>58</v>
       </c>
       <c r="B58">
         <v>12780</v>
       </c>
-      <c r="C58" s="4">
+      <c r="C58" s="2">
         <f t="shared" si="0"/>
         <v>221</v>
       </c>
-      <c r="D58" s="5"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="P58" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q58" s="12"/>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>59</v>
       </c>
       <c r="B59">
         <v>12735</v>
       </c>
-      <c r="C59" s="4">
+      <c r="C59" s="2">
         <f t="shared" si="0"/>
         <v>221</v>
       </c>
-      <c r="D59" s="5"/>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="P59" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q59" s="12"/>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>60</v>
       </c>
       <c r="B60">
         <v>12567</v>
       </c>
-      <c r="C60" s="4">
+      <c r="C60" s="2">
         <f t="shared" si="0"/>
         <v>218</v>
       </c>
-      <c r="D60" s="5"/>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="P60" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q60" s="12"/>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>61</v>
       </c>
       <c r="B61">
         <v>12356</v>
       </c>
-      <c r="C61" s="4">
+      <c r="C61" s="2">
         <f t="shared" si="0"/>
         <v>214</v>
       </c>
-      <c r="D61" s="5"/>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="P61" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q61" s="12"/>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>62</v>
       </c>
       <c r="B62">
         <v>12056</v>
       </c>
-      <c r="C62" s="4">
+      <c r="C62" s="2">
         <f t="shared" si="0"/>
         <v>209</v>
       </c>
-      <c r="D62" s="5"/>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="P62" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q62" s="12"/>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>63</v>
       </c>
       <c r="B63">
         <v>11900</v>
       </c>
-      <c r="C63" s="4">
+      <c r="C63" s="2">
         <f t="shared" si="0"/>
         <v>206</v>
       </c>
-      <c r="D63" s="5"/>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
+      <c r="P63" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q63" s="12"/>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>64</v>
       </c>
       <c r="B64">
         <v>11382</v>
       </c>
-      <c r="C64" s="4">
+      <c r="C64" s="2">
         <f t="shared" si="0"/>
         <v>197</v>
       </c>
-      <c r="D64" s="5"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
+      <c r="P64" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q64" s="12"/>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>65</v>
       </c>
       <c r="B65">
         <v>11295</v>
       </c>
-      <c r="C65" s="4">
+      <c r="C65" s="2">
         <f t="shared" si="0"/>
         <v>196</v>
       </c>
-      <c r="D65" s="5"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3"/>
+      <c r="P65" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q65" s="12"/>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>66</v>
       </c>
       <c r="B66">
         <v>11229</v>
       </c>
-      <c r="C66" s="4">
+      <c r="C66" s="2">
         <f t="shared" si="0"/>
         <v>195</v>
       </c>
-      <c r="D66" s="5"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
+      <c r="P66" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q66" s="12"/>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>67</v>
       </c>
       <c r="B67">
         <v>10960</v>
       </c>
-      <c r="C67" s="4">
-        <f t="shared" ref="C67:C101" si="1">ROUND((B67/5770465)*100000, 0)</f>
+      <c r="C67" s="2">
+        <f t="shared" ref="C67:C101" si="2">ROUND((B67/5770465)*100000, 0)</f>
         <v>190</v>
       </c>
-      <c r="D67" s="5"/>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="P67" s="12" t="str">
+        <f t="shared" ref="P67:P100" si="3">IF(C67&gt;=850, "高風險", IF(C67&gt;=168, "中風險", "低風險"))</f>
+        <v>中風險</v>
+      </c>
+      <c r="Q67" s="12"/>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>68</v>
       </c>
       <c r="B68">
         <v>10860</v>
       </c>
-      <c r="C68" s="4">
-        <f t="shared" si="1"/>
+      <c r="C68" s="2">
+        <f t="shared" si="2"/>
         <v>188</v>
       </c>
-      <c r="D68" s="5"/>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="P68" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q68" s="12"/>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>69</v>
       </c>
       <c r="B69">
         <v>10855</v>
       </c>
-      <c r="C69" s="4">
-        <f t="shared" si="1"/>
+      <c r="C69" s="2">
+        <f t="shared" si="2"/>
         <v>188</v>
       </c>
-      <c r="D69" s="5"/>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="P69" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q69" s="12"/>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>70</v>
       </c>
       <c r="B70">
         <v>10723</v>
       </c>
-      <c r="C70" s="4">
-        <f t="shared" si="1"/>
+      <c r="C70" s="2">
+        <f t="shared" si="2"/>
         <v>186</v>
       </c>
-      <c r="D70" s="5"/>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="P70" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q70" s="12"/>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>71</v>
       </c>
       <c r="B71">
         <v>10471</v>
       </c>
-      <c r="C71" s="4">
-        <f t="shared" si="1"/>
+      <c r="C71" s="2">
+        <f t="shared" si="2"/>
         <v>181</v>
       </c>
-      <c r="D71" s="5"/>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
+      <c r="P71" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q71" s="12"/>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>72</v>
       </c>
       <c r="B72">
         <v>10444</v>
       </c>
-      <c r="C72" s="4">
-        <f t="shared" si="1"/>
+      <c r="C72" s="2">
+        <f t="shared" si="2"/>
         <v>181</v>
       </c>
-      <c r="D72" s="5"/>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+      <c r="P72" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q72" s="12"/>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>73</v>
       </c>
       <c r="B73">
         <v>10147</v>
       </c>
-      <c r="C73" s="4">
-        <f t="shared" si="1"/>
+      <c r="C73" s="2">
+        <f t="shared" si="2"/>
         <v>176</v>
       </c>
-      <c r="D73" s="5"/>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
+      <c r="P73" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q73" s="12"/>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>74</v>
       </c>
       <c r="B74">
         <v>10113</v>
       </c>
-      <c r="C74" s="4">
-        <f t="shared" si="1"/>
+      <c r="C74" s="2">
+        <f t="shared" si="2"/>
         <v>175</v>
       </c>
-      <c r="D74" s="5"/>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3"/>
+      <c r="P74" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q74" s="12"/>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>75</v>
       </c>
       <c r="B75">
         <v>9963</v>
       </c>
-      <c r="C75" s="4">
-        <f t="shared" si="1"/>
+      <c r="C75" s="2">
+        <f t="shared" si="2"/>
         <v>173</v>
       </c>
-      <c r="D75" s="5"/>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
+      <c r="P75" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q75" s="12"/>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>76</v>
       </c>
       <c r="B76">
         <v>9827</v>
       </c>
-      <c r="C76" s="4">
-        <f t="shared" si="1"/>
+      <c r="C76" s="2">
+        <f t="shared" si="2"/>
         <v>170</v>
       </c>
-      <c r="D76" s="5"/>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+      <c r="P76" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>中風險</v>
+      </c>
+      <c r="Q76" s="12"/>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>77</v>
       </c>
       <c r="B77">
         <v>9424</v>
       </c>
-      <c r="C77" s="4">
-        <f t="shared" si="1"/>
+      <c r="C77" s="2">
+        <f t="shared" si="2"/>
         <v>163</v>
       </c>
-      <c r="D77" s="5"/>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
+      <c r="P77" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>低風險</v>
+      </c>
+      <c r="Q77" s="13"/>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>78</v>
       </c>
       <c r="B78">
         <v>9379</v>
       </c>
-      <c r="C78" s="4">
-        <f t="shared" si="1"/>
+      <c r="C78" s="2">
+        <f t="shared" si="2"/>
         <v>163</v>
       </c>
-      <c r="D78" s="5"/>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="P78" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>低風險</v>
+      </c>
+      <c r="Q78" s="13"/>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>79</v>
       </c>
       <c r="B79">
         <v>9306</v>
       </c>
-      <c r="C79" s="4">
-        <f t="shared" si="1"/>
+      <c r="C79" s="2">
+        <f t="shared" si="2"/>
         <v>161</v>
       </c>
-      <c r="D79" s="5"/>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3"/>
+      <c r="P79" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>低風險</v>
+      </c>
+      <c r="Q79" s="13"/>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>80</v>
       </c>
       <c r="B80">
         <v>9284</v>
       </c>
-      <c r="C80" s="4">
-        <f t="shared" si="1"/>
+      <c r="C80" s="2">
+        <f t="shared" si="2"/>
         <v>161</v>
       </c>
-      <c r="D80" s="5"/>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
+      <c r="P80" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>低風險</v>
+      </c>
+      <c r="Q80" s="13"/>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>81</v>
       </c>
       <c r="B81">
         <v>8908</v>
       </c>
-      <c r="C81" s="4">
-        <f t="shared" si="1"/>
+      <c r="C81" s="2">
+        <f t="shared" si="2"/>
         <v>154</v>
       </c>
-      <c r="D81" s="5"/>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3"/>
+      <c r="P81" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>低風險</v>
+      </c>
+      <c r="Q81" s="13"/>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>82</v>
       </c>
       <c r="B82">
         <v>8389</v>
       </c>
-      <c r="C82" s="4">
-        <f t="shared" si="1"/>
+      <c r="C82" s="2">
+        <f t="shared" si="2"/>
         <v>145</v>
       </c>
-      <c r="D82" s="5"/>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
+      <c r="P82" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>低風險</v>
+      </c>
+      <c r="Q82" s="13"/>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>83</v>
       </c>
       <c r="B83">
         <v>8352</v>
       </c>
-      <c r="C83" s="4">
-        <f t="shared" si="1"/>
+      <c r="C83" s="2">
+        <f t="shared" si="2"/>
         <v>145</v>
       </c>
-      <c r="D83" s="5"/>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3"/>
+      <c r="P83" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>低風險</v>
+      </c>
+      <c r="Q83" s="13"/>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>84</v>
       </c>
       <c r="B84">
         <v>8252</v>
       </c>
-      <c r="C84" s="4">
-        <f t="shared" si="1"/>
+      <c r="C84" s="2">
+        <f t="shared" si="2"/>
         <v>143</v>
       </c>
-      <c r="D84" s="5"/>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
+      <c r="P84" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>低風險</v>
+      </c>
+      <c r="Q84" s="13"/>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>85</v>
       </c>
       <c r="B85">
         <v>8193</v>
       </c>
-      <c r="C85" s="4">
-        <f t="shared" si="1"/>
+      <c r="C85" s="2">
+        <f t="shared" si="2"/>
         <v>142</v>
       </c>
-      <c r="D85" s="5"/>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3"/>
+      <c r="P85" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>低風險</v>
+      </c>
+      <c r="Q85" s="13"/>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>86</v>
       </c>
       <c r="B86">
         <v>8126</v>
       </c>
-      <c r="C86" s="4">
-        <f t="shared" si="1"/>
+      <c r="C86" s="2">
+        <f t="shared" si="2"/>
         <v>141</v>
       </c>
-      <c r="D86" s="5"/>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
+      <c r="P86" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>低風險</v>
+      </c>
+      <c r="Q86" s="13"/>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>87</v>
       </c>
       <c r="B87">
         <v>7993</v>
       </c>
-      <c r="C87" s="4">
-        <f t="shared" si="1"/>
+      <c r="C87" s="2">
+        <f t="shared" si="2"/>
         <v>139</v>
       </c>
-      <c r="D87" s="5"/>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
+      <c r="P87" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>低風險</v>
+      </c>
+      <c r="Q87" s="13"/>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>88</v>
       </c>
       <c r="B88">
         <v>7966</v>
       </c>
-      <c r="C88" s="4">
-        <f t="shared" si="1"/>
+      <c r="C88" s="2">
+        <f t="shared" si="2"/>
         <v>138</v>
       </c>
-      <c r="D88" s="5"/>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
+      <c r="P88" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>低風險</v>
+      </c>
+      <c r="Q88" s="13"/>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>89</v>
       </c>
       <c r="B89">
         <v>7817</v>
       </c>
-      <c r="C89" s="4">
-        <f t="shared" si="1"/>
+      <c r="C89" s="2">
+        <f t="shared" si="2"/>
         <v>135</v>
       </c>
-      <c r="D89" s="5"/>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
+      <c r="P89" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>低風險</v>
+      </c>
+      <c r="Q89" s="13"/>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>90</v>
       </c>
       <c r="B90">
         <v>7796</v>
       </c>
-      <c r="C90" s="4">
-        <f t="shared" si="1"/>
+      <c r="C90" s="2">
+        <f t="shared" si="2"/>
         <v>135</v>
       </c>
-      <c r="D90" s="5"/>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+      <c r="P90" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>低風險</v>
+      </c>
+      <c r="Q90" s="13"/>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>91</v>
       </c>
       <c r="B91">
         <v>7739</v>
       </c>
-      <c r="C91" s="4">
-        <f t="shared" si="1"/>
+      <c r="C91" s="2">
+        <f t="shared" si="2"/>
         <v>134</v>
       </c>
-      <c r="D91" s="5"/>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
+      <c r="P91" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>低風險</v>
+      </c>
+      <c r="Q91" s="13"/>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>92</v>
       </c>
       <c r="B92">
         <v>7640</v>
       </c>
-      <c r="C92" s="4">
-        <f t="shared" si="1"/>
+      <c r="C92" s="2">
+        <f t="shared" si="2"/>
         <v>132</v>
       </c>
-      <c r="D92" s="5"/>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
+      <c r="P92" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>低風險</v>
+      </c>
+      <c r="Q92" s="13"/>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>93</v>
       </c>
       <c r="B93">
         <v>7480</v>
       </c>
-      <c r="C93" s="4">
-        <f t="shared" si="1"/>
+      <c r="C93" s="2">
+        <f t="shared" si="2"/>
         <v>130</v>
       </c>
-      <c r="D93" s="5"/>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
+      <c r="P93" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>低風險</v>
+      </c>
+      <c r="Q93" s="13"/>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>94</v>
       </c>
       <c r="B94">
         <v>7475</v>
       </c>
-      <c r="C94" s="4">
-        <f t="shared" si="1"/>
+      <c r="C94" s="2">
+        <f t="shared" si="2"/>
         <v>130</v>
       </c>
-      <c r="D94" s="5"/>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
+      <c r="P94" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>低風險</v>
+      </c>
+      <c r="Q94" s="13"/>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>95</v>
       </c>
       <c r="B95">
         <v>7428</v>
       </c>
-      <c r="C95" s="4">
-        <f t="shared" si="1"/>
+      <c r="C95" s="2">
+        <f t="shared" si="2"/>
         <v>129</v>
       </c>
-      <c r="D95" s="5"/>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
+      <c r="P95" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>低風險</v>
+      </c>
+      <c r="Q95" s="13"/>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>96</v>
       </c>
       <c r="B96">
         <v>7344</v>
       </c>
-      <c r="C96" s="4">
-        <f t="shared" si="1"/>
+      <c r="C96" s="2">
+        <f t="shared" si="2"/>
         <v>127</v>
       </c>
-      <c r="D96" s="5"/>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
+      <c r="P96" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>低風險</v>
+      </c>
+      <c r="Q96" s="13"/>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>97</v>
       </c>
       <c r="B97">
         <v>6936</v>
       </c>
-      <c r="C97" s="4">
-        <f t="shared" si="1"/>
+      <c r="C97" s="2">
+        <f t="shared" si="2"/>
         <v>120</v>
       </c>
-      <c r="D97" s="5"/>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
+      <c r="P97" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>低風險</v>
+      </c>
+      <c r="Q97" s="13"/>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>98</v>
       </c>
       <c r="B98">
         <v>6892</v>
       </c>
-      <c r="C98" s="4">
-        <f t="shared" si="1"/>
+      <c r="C98" s="2">
+        <f t="shared" si="2"/>
         <v>119</v>
       </c>
-      <c r="D98" s="5"/>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+      <c r="P98" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>低風險</v>
+      </c>
+      <c r="Q98" s="13"/>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>99</v>
       </c>
       <c r="B99">
         <v>6842</v>
       </c>
-      <c r="C99" s="4">
-        <f t="shared" si="1"/>
+      <c r="C99" s="2">
+        <f t="shared" si="2"/>
         <v>119</v>
       </c>
-      <c r="D99" s="5"/>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
+      <c r="P99" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>低風險</v>
+      </c>
+      <c r="Q99" s="13"/>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>100</v>
       </c>
       <c r="B100">
         <v>6696</v>
       </c>
-      <c r="C100" s="4">
-        <f t="shared" si="1"/>
+      <c r="C100" s="2">
+        <f t="shared" si="2"/>
         <v>116</v>
       </c>
-      <c r="D100" s="5"/>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
+      <c r="P100" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>低風險</v>
+      </c>
+      <c r="Q100" s="13"/>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>101</v>
       </c>
       <c r="B101">
         <v>6686</v>
       </c>
-      <c r="C101" s="4">
-        <f t="shared" si="1"/>
+      <c r="C101" s="2">
+        <f t="shared" si="2"/>
         <v>116</v>
       </c>
-      <c r="D101" s="5"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3"/>
+      <c r="P101" s="6"/>
+      <c r="Q101" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="101">
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
+  <mergeCells count="107">
+    <mergeCell ref="P99:Q99"/>
+    <mergeCell ref="P100:Q100"/>
+    <mergeCell ref="P101:Q101"/>
+    <mergeCell ref="P90:Q90"/>
+    <mergeCell ref="P91:Q91"/>
+    <mergeCell ref="P92:Q92"/>
+    <mergeCell ref="P93:Q93"/>
+    <mergeCell ref="P94:Q94"/>
+    <mergeCell ref="P95:Q95"/>
+    <mergeCell ref="P96:Q96"/>
+    <mergeCell ref="P97:Q97"/>
+    <mergeCell ref="P98:Q98"/>
+    <mergeCell ref="P81:Q81"/>
+    <mergeCell ref="P82:Q82"/>
+    <mergeCell ref="P83:Q83"/>
+    <mergeCell ref="P84:Q84"/>
+    <mergeCell ref="P85:Q85"/>
+    <mergeCell ref="P86:Q86"/>
+    <mergeCell ref="P87:Q87"/>
+    <mergeCell ref="P88:Q88"/>
+    <mergeCell ref="P89:Q89"/>
+    <mergeCell ref="P72:Q72"/>
+    <mergeCell ref="P73:Q73"/>
+    <mergeCell ref="P74:Q74"/>
+    <mergeCell ref="P75:Q75"/>
+    <mergeCell ref="P76:Q76"/>
+    <mergeCell ref="P77:Q77"/>
+    <mergeCell ref="P78:Q78"/>
+    <mergeCell ref="P79:Q79"/>
+    <mergeCell ref="P80:Q80"/>
+    <mergeCell ref="P63:Q63"/>
+    <mergeCell ref="P64:Q64"/>
+    <mergeCell ref="P65:Q65"/>
+    <mergeCell ref="P66:Q66"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="P68:Q68"/>
+    <mergeCell ref="P69:Q69"/>
+    <mergeCell ref="P70:Q70"/>
+    <mergeCell ref="P71:Q71"/>
+    <mergeCell ref="P54:Q54"/>
+    <mergeCell ref="P55:Q55"/>
+    <mergeCell ref="P56:Q56"/>
+    <mergeCell ref="P57:Q57"/>
+    <mergeCell ref="P58:Q58"/>
+    <mergeCell ref="P59:Q59"/>
+    <mergeCell ref="P60:Q60"/>
+    <mergeCell ref="P61:Q61"/>
+    <mergeCell ref="P62:Q62"/>
+    <mergeCell ref="P45:Q45"/>
+    <mergeCell ref="P46:Q46"/>
+    <mergeCell ref="P47:Q47"/>
+    <mergeCell ref="P48:Q48"/>
+    <mergeCell ref="P49:Q49"/>
+    <mergeCell ref="P50:Q50"/>
+    <mergeCell ref="P51:Q51"/>
+    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="P53:Q53"/>
+    <mergeCell ref="P36:Q36"/>
+    <mergeCell ref="P37:Q37"/>
+    <mergeCell ref="P38:Q38"/>
+    <mergeCell ref="P39:Q39"/>
+    <mergeCell ref="P40:Q40"/>
+    <mergeCell ref="P41:Q41"/>
+    <mergeCell ref="P42:Q42"/>
+    <mergeCell ref="P43:Q43"/>
+    <mergeCell ref="P44:Q44"/>
+    <mergeCell ref="P27:Q27"/>
+    <mergeCell ref="P28:Q28"/>
+    <mergeCell ref="P29:Q29"/>
+    <mergeCell ref="P30:Q30"/>
+    <mergeCell ref="P31:Q31"/>
+    <mergeCell ref="P32:Q32"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="P34:Q34"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="P25:Q25"/>
+    <mergeCell ref="P26:Q26"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="H1:K1"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="L1:O1"/>
+    <mergeCell ref="L2:O2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/100_keywords_freq.xlsx
+++ b/100_keywords_freq.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0909\web---vue_backup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF56F35C-2E6F-49A3-94B6-5983EE525577}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF3C3661-ED4B-4F73-9092-9CDFAAE53F36}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17268" windowHeight="5496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3052,8 +3052,11 @@
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
       <c r="G101" s="3"/>
-      <c r="P101" s="6"/>
-      <c r="Q101" s="6"/>
+      <c r="P101" s="13" t="str">
+        <f t="shared" ref="P101" si="4">IF(C101&gt;=850, "高風險", IF(C101&gt;=168, "中風險", "低風險"))</f>
+        <v>低風險</v>
+      </c>
+      <c r="Q101" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="107">
